--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0001T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.73257847612694</v>
+        <v>7.269044002370628</v>
       </c>
       <c r="D2" t="n">
-        <v>25.67825940224232</v>
+        <v>4.172717152864378</v>
       </c>
       <c r="E2" t="n">
-        <v>10.56462136960848</v>
+        <v>1.716750972561378</v>
       </c>
       <c r="F2" t="n">
-        <v>10.35509616669146</v>
+        <v>1.682703127087362</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.23154621172782</v>
+        <v>2.475126259405771</v>
       </c>
       <c r="D3" t="n">
-        <v>34.86063084292137</v>
+        <v>5.664852511974722</v>
       </c>
       <c r="E3" t="n">
-        <v>10.56462136960848</v>
+        <v>1.716750972561378</v>
       </c>
       <c r="F3" t="n">
-        <v>10.35509616669146</v>
+        <v>1.682703127087362</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>20.55480479109447</v>
+        <v>3.340155778552851</v>
       </c>
       <c r="D4" t="n">
-        <v>13.16679428523256</v>
+        <v>2.139604071350291</v>
       </c>
       <c r="E4" t="n">
-        <v>10.56462136960848</v>
+        <v>1.716750972561378</v>
       </c>
       <c r="F4" t="n">
-        <v>10.35509616669146</v>
+        <v>1.682703127087362</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>23.96195755010514</v>
+        <v>3.893818101892085</v>
       </c>
       <c r="D5" t="n">
-        <v>21.32417681994272</v>
+        <v>3.465178733240693</v>
       </c>
       <c r="E5" t="n">
-        <v>10.56462136960848</v>
+        <v>1.716750972561378</v>
       </c>
       <c r="F5" t="n">
-        <v>10.35509616669146</v>
+        <v>1.682703127087362</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.50609665440988</v>
+        <v>3.332240706341605</v>
       </c>
       <c r="D6" t="n">
-        <v>18.66721971317007</v>
+        <v>3.033423203390136</v>
       </c>
       <c r="E6" t="n">
-        <v>10.56462136960848</v>
+        <v>1.716750972561378</v>
       </c>
       <c r="F6" t="n">
-        <v>10.35509616669146</v>
+        <v>1.682703127087362</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.32923534688643</v>
+        <v>4.441000743869044</v>
       </c>
       <c r="D7" t="n">
-        <v>7.048916554965155</v>
+        <v>1.145448940181838</v>
       </c>
       <c r="E7" t="n">
-        <v>10.56462136960848</v>
+        <v>1.716750972561378</v>
       </c>
       <c r="F7" t="n">
-        <v>10.35509616669146</v>
+        <v>1.682703127087362</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.276472678623424</v>
+        <v>1.344926810276307</v>
       </c>
       <c r="D8" t="n">
-        <v>2.06155281280883</v>
+        <v>0.3350023320814349</v>
       </c>
       <c r="E8" t="n">
-        <v>10.56462136960848</v>
+        <v>1.716750972561378</v>
       </c>
       <c r="F8" t="n">
-        <v>10.35509616669146</v>
+        <v>1.682703127087362</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
